--- a/Result/profitability/5607.xlsx
+++ b/Result/profitability/5607.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM79"/>
+  <dimension ref="A1:AM80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,10 +667,10 @@
         <v>0.37</v>
       </c>
       <c r="M2" t="n">
-        <v>0.65625</v>
+        <v>0.72625</v>
       </c>
       <c r="N2" t="n">
-        <v>22.47375</v>
+        <v>23.26374999999999</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -776,10 +776,10 @@
         <v>-0.6</v>
       </c>
       <c r="M3" t="n">
-        <v>0.50125</v>
+        <v>0.5925</v>
       </c>
       <c r="N3" t="n">
-        <v>19.1875</v>
+        <v>20.2825</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -893,10 +893,10 @@
         <v>-0.62</v>
       </c>
       <c r="M4" t="n">
-        <v>0.365</v>
+        <v>0.45</v>
       </c>
       <c r="N4" t="n">
-        <v>17.28</v>
+        <v>18.0375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1010,10 +1010,10 @@
         <v>-0.23</v>
       </c>
       <c r="M5" t="n">
-        <v>0.27125</v>
+        <v>0.32125</v>
       </c>
       <c r="N5" t="n">
-        <v>15.32875</v>
+        <v>15.8775</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1127,10 +1127,10 @@
         <v>-0.53</v>
       </c>
       <c r="M6" t="n">
-        <v>0.105</v>
+        <v>0.1525</v>
       </c>
       <c r="N6" t="n">
-        <v>14.185</v>
+        <v>14.35</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1254,10 +1254,10 @@
         <v>1.88</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2375</v>
+        <v>0.30625</v>
       </c>
       <c r="N7" t="n">
-        <v>16.81875</v>
+        <v>17.73875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1381,10 +1381,10 @@
         <v>0.32</v>
       </c>
       <c r="M8" t="n">
-        <v>0.19625</v>
+        <v>0.22375</v>
       </c>
       <c r="N8" t="n">
-        <v>18.09</v>
+        <v>18.4775</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1508,7 +1508,7 @@
         <v>-0.24</v>
       </c>
       <c r="M9" t="n">
-        <v>0.04374999999999999</v>
+        <v>0.04375</v>
       </c>
       <c r="N9" t="n">
         <v>16.38375</v>
@@ -1638,7 +1638,7 @@
         <v>-0.065</v>
       </c>
       <c r="N10" t="n">
-        <v>41.25000000000001</v>
+        <v>41.25</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1762,10 +1762,10 @@
         <v>-0.3</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.02750000000000001</v>
+        <v>-0.0275</v>
       </c>
       <c r="N11" t="n">
-        <v>41.515</v>
+        <v>41.51499999999999</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1889,7 +1889,7 @@
         <v>-0.22</v>
       </c>
       <c r="M12" t="n">
-        <v>0.02249999999999999</v>
+        <v>0.0225</v>
       </c>
       <c r="N12" t="n">
         <v>42.3425</v>
@@ -2016,7 +2016,7 @@
         <v>-0.18</v>
       </c>
       <c r="M13" t="n">
-        <v>0.02874999999999999</v>
+        <v>0.02875</v>
       </c>
       <c r="N13" t="n">
         <v>42.54625</v>
@@ -2273,7 +2273,7 @@
         <v>-0.1675</v>
       </c>
       <c r="N15" t="n">
-        <v>37.63875</v>
+        <v>37.63874999999999</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
@@ -10455,6 +10455,133 @@
       </c>
       <c r="AM79" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>5607</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1370</v>
+      </c>
+      <c r="D80" t="n">
+        <v>624</v>
+      </c>
+      <c r="E80" t="n">
+        <v>745</v>
+      </c>
+      <c r="F80" t="n">
+        <v>54.43</v>
+      </c>
+      <c r="G80" t="n">
+        <v>647</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>47.27%</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>-84</v>
+      </c>
+      <c r="J80" t="n">
+        <v>563</v>
+      </c>
+      <c r="K80" t="n">
+        <v>445</v>
+      </c>
+      <c r="L80" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="N80" t="n">
+        <v>49.76625</v>
+      </c>
+      <c r="O80" t="n">
+        <v>1</v>
+      </c>
+      <c r="P80" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>1</v>
+      </c>
+      <c r="R80" t="n">
+        <v>1</v>
+      </c>
+      <c r="S80" t="n">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>1</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1</v>
+      </c>
+      <c r="V80" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W80" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="X80" t="n">
+        <v>0.2244897959183674</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>3.100000000000001</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>0.0603935320475355</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>0.4999999999999998</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>4.390000000000001</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>0.08772981614708231</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK80" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL80" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM80" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
